--- a/Lander DB 251 redux.xlsx
+++ b/Lander DB 251 redux.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA ACTA Paper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB38BB50-8680-4FF7-93F4-6A3092D50F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82E896B-1E59-4071-BF18-F4ADC46058B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Real Landers" sheetId="1" r:id="rId1"/>
@@ -1445,7 +1445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1476,6 +1476,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1801,20 +1804,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1852,7 +1855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="11">
         <v>1966</v>
       </c>
@@ -1895,7 +1898,7 @@
       </c>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -1938,7 +1941,7 @@
       </c>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -1980,7 +1983,7 @@
       </c>
       <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -2022,7 +2025,7 @@
       </c>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -2064,7 +2067,7 @@
       </c>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -2106,7 +2109,7 @@
       </c>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -2148,7 +2151,7 @@
       </c>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1969</v>
       </c>
@@ -2191,7 +2194,7 @@
       </c>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>1969</v>
       </c>
@@ -2234,7 +2237,7 @@
       </c>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1970</v>
       </c>
@@ -2277,7 +2280,7 @@
       </c>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -2320,7 +2323,7 @@
       </c>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1970</v>
       </c>
@@ -2363,7 +2366,7 @@
       </c>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>1971</v>
       </c>
@@ -2406,7 +2409,7 @@
       </c>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>1971</v>
       </c>
@@ -2449,7 +2452,7 @@
       </c>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>1972</v>
       </c>
@@ -2492,7 +2495,7 @@
       </c>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -2535,7 +2538,7 @@
       </c>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -2578,7 +2581,7 @@
       </c>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -2615,7 +2618,7 @@
       </c>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -2658,7 +2661,7 @@
       </c>
       <c r="M20" s="4"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -2699,7 +2702,7 @@
       </c>
       <c r="M21" s="4"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -2740,7 +2743,7 @@
       </c>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -2779,7 +2782,7 @@
       </c>
       <c r="M23" s="4"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -2820,7 +2823,7 @@
       </c>
       <c r="M24" s="4"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -2861,7 +2864,7 @@
       </c>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -2900,7 +2903,7 @@
       </c>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -2939,7 +2942,7 @@
       </c>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -2977,7 +2980,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>2023</v>
       </c>
@@ -3004,7 +3007,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -3014,14 +3017,14 @@
       <c r="C30" s="5">
         <v>1908</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="14">
         <f>675-E30</f>
         <v>545</v>
       </c>
       <c r="E30" s="5">
         <v>130</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="14">
         <v>1276</v>
       </c>
       <c r="G30" s="5">
@@ -3037,7 +3040,7 @@
       <c r="J30" s="10"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>2024</v>
       </c>
@@ -3064,7 +3067,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -3104,7 +3107,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>2024</v>
       </c>
@@ -3144,9 +3147,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB6D447-256B-4552-8531-20A905B8B356}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3184,7 +3187,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -3226,7 +3229,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -3268,7 +3271,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -3309,7 +3312,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -3350,7 +3353,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -3391,7 +3394,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -3432,7 +3435,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -3473,7 +3476,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1970</v>
       </c>
@@ -3515,7 +3518,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>1970</v>
       </c>
@@ -3557,7 +3560,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1972</v>
       </c>
@@ -3599,7 +3602,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1973</v>
       </c>
@@ -3641,7 +3644,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1976</v>
       </c>
@@ -3683,7 +3686,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>2013</v>
       </c>
@@ -3723,7 +3726,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>2019</v>
       </c>
@@ -3763,7 +3766,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2019</v>
       </c>
@@ -3801,7 +3804,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>2019</v>
       </c>
@@ -3841,7 +3844,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>2020</v>
       </c>
@@ -3881,7 +3884,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>2022</v>
       </c>
@@ -3919,7 +3922,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>2023</v>
       </c>
@@ -3957,7 +3960,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>2023</v>
       </c>
@@ -3995,7 +3998,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -4035,7 +4038,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -4120,9 +4123,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05661A04-FF2A-413A-B709-071725466C45}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4160,7 +4163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -4202,7 +4205,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -4244,7 +4247,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -4285,7 +4288,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1970</v>
       </c>
@@ -4327,7 +4330,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1970</v>
       </c>
@@ -4369,7 +4372,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1973</v>
       </c>
@@ -4411,7 +4414,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1976</v>
       </c>
@@ -4453,7 +4456,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>2019</v>
       </c>
@@ -4491,7 +4494,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>2019</v>
       </c>
@@ -4531,7 +4534,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>2020</v>
       </c>
@@ -4571,7 +4574,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>2022</v>
       </c>
@@ -4609,7 +4612,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>2023</v>
       </c>
@@ -4647,7 +4650,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>2023</v>
       </c>
@@ -4685,7 +4688,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -4725,7 +4728,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2024</v>
       </c>

--- a/Lander DB 251 redux.xlsx
+++ b/Lander DB 251 redux.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82E896B-1E59-4071-BF18-F4ADC46058B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45265BF0-BF18-4C71-AA97-11B76F695737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1445,7 +1445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1476,9 +1476,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1804,20 +1801,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1855,7 +1852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1966</v>
       </c>
@@ -1898,7 +1895,7 @@
       </c>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -1941,7 +1938,7 @@
       </c>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -1983,7 +1980,7 @@
       </c>
       <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -2025,7 +2022,7 @@
       </c>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -2067,7 +2064,7 @@
       </c>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -2109,7 +2106,7 @@
       </c>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -2151,7 +2148,7 @@
       </c>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>1969</v>
       </c>
@@ -2194,7 +2191,7 @@
       </c>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>1969</v>
       </c>
@@ -2237,7 +2234,7 @@
       </c>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1970</v>
       </c>
@@ -2280,7 +2277,7 @@
       </c>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -2323,7 +2320,7 @@
       </c>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>1970</v>
       </c>
@@ -2366,7 +2363,7 @@
       </c>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>1971</v>
       </c>
@@ -2409,7 +2406,7 @@
       </c>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>1971</v>
       </c>
@@ -2452,7 +2449,7 @@
       </c>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>1972</v>
       </c>
@@ -2495,7 +2492,7 @@
       </c>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -2538,7 +2535,7 @@
       </c>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -2581,7 +2578,7 @@
       </c>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -2618,7 +2615,7 @@
       </c>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -2661,7 +2658,7 @@
       </c>
       <c r="M20" s="4"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -2702,7 +2699,7 @@
       </c>
       <c r="M21" s="4"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -2743,7 +2740,7 @@
       </c>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -2782,7 +2779,7 @@
       </c>
       <c r="M23" s="4"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -2823,7 +2820,7 @@
       </c>
       <c r="M24" s="4"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -2864,7 +2861,7 @@
       </c>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -2903,7 +2900,7 @@
       </c>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -2942,7 +2939,7 @@
       </c>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -2980,7 +2977,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2023</v>
       </c>
@@ -3007,7 +3004,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -3017,14 +3014,14 @@
       <c r="C30" s="5">
         <v>1908</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="8">
         <f>675-E30</f>
         <v>545</v>
       </c>
       <c r="E30" s="5">
         <v>130</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F30" s="8">
         <v>1276</v>
       </c>
       <c r="G30" s="5">
@@ -3040,7 +3037,7 @@
       <c r="J30" s="10"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>2024</v>
       </c>
@@ -3067,7 +3064,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -3107,7 +3104,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <v>2024</v>
       </c>
@@ -3147,9 +3144,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB6D447-256B-4552-8531-20A905B8B356}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3187,7 +3184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -3229,7 +3226,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -3271,7 +3268,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -3312,7 +3309,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -3353,7 +3350,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -3394,7 +3391,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -3435,7 +3432,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -3476,7 +3473,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>1970</v>
       </c>
@@ -3518,7 +3515,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>1970</v>
       </c>
@@ -3560,7 +3557,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1972</v>
       </c>
@@ -3602,7 +3599,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1973</v>
       </c>
@@ -3644,7 +3641,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>1976</v>
       </c>
@@ -3686,7 +3683,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>2013</v>
       </c>
@@ -3726,7 +3723,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>2019</v>
       </c>
@@ -3766,7 +3763,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2019</v>
       </c>
@@ -3804,7 +3801,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>2019</v>
       </c>
@@ -3844,7 +3841,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>2020</v>
       </c>
@@ -3884,7 +3881,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>2022</v>
       </c>
@@ -3922,7 +3919,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>2023</v>
       </c>
@@ -3960,7 +3957,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>2023</v>
       </c>
@@ -3998,7 +3995,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -4038,7 +4035,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -4123,9 +4120,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05661A04-FF2A-413A-B709-071725466C45}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4163,7 +4160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -4205,7 +4202,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -4247,7 +4244,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -4288,7 +4285,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1970</v>
       </c>
@@ -4330,7 +4327,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>1970</v>
       </c>
@@ -4372,7 +4369,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1973</v>
       </c>
@@ -4414,7 +4411,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1976</v>
       </c>
@@ -4456,7 +4453,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2019</v>
       </c>
@@ -4494,7 +4491,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>2019</v>
       </c>
@@ -4534,7 +4531,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>2020</v>
       </c>
@@ -4574,7 +4571,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>2022</v>
       </c>
@@ -4612,7 +4609,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>2023</v>
       </c>
@@ -4650,7 +4647,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>2023</v>
       </c>
@@ -4688,7 +4685,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -4728,7 +4725,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2024</v>
       </c>

--- a/Lander DB 251 redux.xlsx
+++ b/Lander DB 251 redux.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45265BF0-BF18-4C71-AA97-11B76F695737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9D9499-E3FE-42F7-9CAD-38351E354CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Real Landers" sheetId="1" r:id="rId1"/>
-    <sheet name="All Real Unmanned Landers" sheetId="2" r:id="rId2"/>
-    <sheet name="Just models" sheetId="3" r:id="rId3"/>
+    <sheet name="Feuil1" sheetId="4" r:id="rId2"/>
+    <sheet name="All Real Unmanned Landers" sheetId="2" r:id="rId3"/>
+    <sheet name="Just models" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -399,56 +400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D29" authorId="0" shapeId="0" xr:uid="{8A36D727-4922-47F8-8952-30867B88E13E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Conall DE PAOR:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-inferred from resultant dV of chandrayaan 2. assuming same Isp
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J29" authorId="0" shapeId="0" xr:uid="{9395E52A-6746-46B8-97BB-8D404B8ACCD6}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Conall DE PAOR:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-assumed the same as chandrayaan 2. same mission profile</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{BBB5C1D0-7DD5-4E44-A4BA-232EF8D10EE2}">
+    <comment ref="J30" authorId="0" shapeId="0" xr:uid="{BBB5C1D0-7DD5-4E44-A4BA-232EF8D10EE2}">
       <text>
         <r>
           <rPr>
@@ -477,6 +429,445 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Conall DE PAOR</author>
+    <author>tc={F43BA908-11C1-4486-9AC9-41BED78EF776}</author>
+    <author>Conall De Paor</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{118F50EB-C5EC-4A63-8FD7-077B5C379774}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+m_total - m_p - m_prop</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{F43BA908-11C1-4486-9AC9-41BED78EF776}">
+      <text>
+        <t>[Commentaire à thread]
+Votre version d’Excel vous permet de lire ce commentaire à thread. Toutefois, les modifications qui y sont apportées seront supprimées si le fichier est ouvert dans une version plus récente d’Excel. En savoir plus : https://go.microsoft.com/fwlink/?linkid=870924
+Commentaire :
+    bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
+2stage manned landers: ascent stage mass
+1stage manned landers: landed mass
+2stage unmanned landers: ascent stage mass +payload
+1stage unmanned landers: payload</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{4B34D8DF-0F6D-4AD3-8B2B-545F2BAFB198}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+often listed as landed mass</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="2" shapeId="0" xr:uid="{E7E3A4DB-37AA-47A2-A251-864FF83CF6B0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall De Paor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+weight of the pod is considered as the payload because that makes it more comparable</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="2" shapeId="0" xr:uid="{34FFCA51-DBC1-4417-9C71-EC3534F86C60}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall De Paor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+weight of whole pod is considered as the payloadl
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{2638958B-4796-46A4-BE38-4BA0C87342C9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+quoted as landed mass in the literature
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{17FE65AD-0888-400B-8275-2CCA7D2C9A88}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Huntress pg. 222</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{226BDF04-68AF-439D-866C-946723FBEF4B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+NSSDC
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{0B5C07EA-0631-4FFB-ADE8-1E9D60199020}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+quoted as landed mass in the literature
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I21" authorId="2" shapeId="0" xr:uid="{5055D07E-FB7E-4E54-A9DE-5D5BC7499593}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall De Paor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+typical Isp for that fuel</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C22" authorId="2" shapeId="0" xr:uid="{1AD89E3F-B071-4890-A093-CFF9CDAA0B37}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall De Paor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Krebs, Gunter D. “Chang'e 3, 4 (CE 3, 4) / Yutu 1, 2”. Gunter's Space Page. Retrieved December 06, 2022, from https://space.skyrocket.de/doc_sdat/change-3.htm</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="2" shapeId="0" xr:uid="{3063B9F3-68A4-4A2F-8EB5-A76C58B00971}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall De Paor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+https://nssdc.gsfc.nasa.gov/nmc/spacecraft/display.action?id=2018-103A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{222C2F4F-0FE2-4D95-886C-21D8078F02CC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+inferrable from mass properties</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{BE344809-DB50-4BB5-9100-AEB307E3438B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+inferred from mass properties
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I28" authorId="2" shapeId="0" xr:uid="{61C289E1-1904-4737-8599-4B8B604F79A5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall De Paor:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+typical ISP of that fuel
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D29" authorId="0" shapeId="0" xr:uid="{A1A94A72-09D4-4449-BF0C-66C51BB0C21C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+inferred from resultant dV of chandrayaan 2. assuming same Isp
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="0" shapeId="0" xr:uid="{921E7DF2-5DFC-4CF2-A1A9-385E2A647BBA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+assumed the same as chandrayaan 2. same mission profile</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{8BC0D484-7C82-4BA6-9C9B-007B98BA7F8F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Conall DE PAOR:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+inferred from mission analysis</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Conall DE PAOR</author>
@@ -866,7 +1257,7 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Conall DE PAOR</author>
@@ -1160,7 +1551,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="59">
   <si>
     <t>year</t>
   </si>
@@ -1321,9 +1712,6 @@
     <t>LCH4/LOX</t>
   </si>
   <si>
-    <t>Chang'e 6</t>
-  </si>
-  <si>
     <t>model</t>
   </si>
   <si>
@@ -1346,7 +1734,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1366,6 +1754,12 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1776,6 +2170,18 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="E1" dT="2022-08-26T15:20:54.08" personId="{27A20534-E0E1-43F4-B688-BEFF110E20FD}" id="{F43BA908-11C1-4486-9AC9-41BED78EF776}">
+    <text>bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
+2stage manned landers: ascent stage mass
+1stage manned landers: landed mass
+2stage unmanned landers: ascent stage mass +payload
+1stage unmanned landers: payload</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="E1" dT="2022-08-26T15:20:54.08" personId="{27A20534-E0E1-43F4-B688-BEFF110E20FD}" id="{B3F7CD30-2CE1-4425-828F-964D49209C6F}">
     <text>bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
 2stage manned landers: ascent stage mass
@@ -1786,7 +2192,7 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="E1" dT="2022-08-26T15:20:54.08" personId="{27A20534-E0E1-43F4-B688-BEFF110E20FD}" id="{1825771D-96A2-4E7C-B107-0F2AD72E57AE}">
     <text>bloc payload is an invented quantity to make 2stage manned landers, 1stage manned landers and 1stage unmanned landers comparable. it's definition is the following
@@ -1800,41 +2206,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -1852,7 +2258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="11">
         <v>1966</v>
       </c>
@@ -1895,7 +2301,7 @@
       </c>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -1938,7 +2344,7 @@
       </c>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -1980,7 +2386,7 @@
       </c>
       <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -2022,7 +2428,7 @@
       </c>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -2064,7 +2470,7 @@
       </c>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -2106,7 +2512,7 @@
       </c>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -2148,7 +2554,7 @@
       </c>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1969</v>
       </c>
@@ -2191,7 +2597,7 @@
       </c>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>1969</v>
       </c>
@@ -2234,7 +2640,7 @@
       </c>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1970</v>
       </c>
@@ -2277,7 +2683,7 @@
       </c>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -2320,7 +2726,7 @@
       </c>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1970</v>
       </c>
@@ -2363,7 +2769,7 @@
       </c>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>1971</v>
       </c>
@@ -2406,7 +2812,7 @@
       </c>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>1971</v>
       </c>
@@ -2449,7 +2855,7 @@
       </c>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>1972</v>
       </c>
@@ -2492,7 +2898,7 @@
       </c>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -2535,7 +2941,7 @@
       </c>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -2578,7 +2984,7 @@
       </c>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -2615,7 +3021,7 @@
       </c>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -2658,7 +3064,7 @@
       </c>
       <c r="M20" s="4"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -2699,7 +3105,7 @@
       </c>
       <c r="M21" s="4"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -2740,7 +3146,7 @@
       </c>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -2779,7 +3185,7 @@
       </c>
       <c r="M23" s="4"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -2820,7 +3226,7 @@
       </c>
       <c r="M24" s="4"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -2861,7 +3267,7 @@
       </c>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -2900,7 +3306,7 @@
       </c>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -2939,7 +3345,7 @@
       </c>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -2977,7 +3383,1251 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1908</v>
+      </c>
+      <c r="D29" s="8">
+        <f>675-E29</f>
+        <v>545</v>
+      </c>
+      <c r="E29" s="5">
+        <v>130</v>
+      </c>
+      <c r="F29" s="8">
+        <v>1276</v>
+      </c>
+      <c r="G29" s="5">
+        <f>675</f>
+        <v>675</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I29" s="5">
+        <v>360</v>
+      </c>
+      <c r="J29" s="10"/>
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="5">
+        <v>710</v>
+      </c>
+      <c r="D30" s="5">
+        <v>190</v>
+      </c>
+      <c r="E30" s="5">
+        <v>20</v>
+      </c>
+      <c r="F30" s="5">
+        <v>500</v>
+      </c>
+      <c r="G30" s="5">
+        <v>210</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I30" s="5">
+        <v>328</v>
+      </c>
+      <c r="J30" s="5">
+        <v>2774</v>
+      </c>
+      <c r="K30" s="3">
+        <f>E30/D30</f>
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="L30" s="3">
+        <f>E30/(D30+E30)</f>
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L30">
+    <sortCondition ref="A2:A30"/>
+  </sortState>
+  <conditionalFormatting sqref="K2:K30">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B5FE63-1677-42A4-8B75-DD4C8D8979A4}">
+  <dimension ref="A1:L32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="11">
+        <v>1966</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="11">
+        <v>1620</v>
+      </c>
+      <c r="D2" s="11">
+        <v>800</v>
+      </c>
+      <c r="E2" s="11">
+        <v>112</v>
+      </c>
+      <c r="F2" s="11">
+        <f t="shared" ref="F2:F12" si="0">C2-D2-E2</f>
+        <v>708</v>
+      </c>
+      <c r="G2" s="11">
+        <f>C2-F2</f>
+        <v>912</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="11">
+        <v>287</v>
+      </c>
+      <c r="J2" s="11">
+        <v>1880</v>
+      </c>
+      <c r="K2" s="3">
+        <f t="shared" ref="K2:K28" si="1">E2/D2</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L2" s="3">
+        <f t="shared" ref="L2:L28" si="2">E2/(D2+E2)</f>
+        <v>0.12280701754385964</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>1966</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1538</v>
+      </c>
+      <c r="D3" s="8">
+        <v>847</v>
+      </c>
+      <c r="E3" s="8">
+        <v>99.8</v>
+      </c>
+      <c r="F3" s="8">
+        <f t="shared" si="0"/>
+        <v>591.20000000000005</v>
+      </c>
+      <c r="G3" s="8">
+        <f>C3-F3</f>
+        <v>946.8</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="8">
+        <v>287</v>
+      </c>
+      <c r="J3" s="8">
+        <v>2630</v>
+      </c>
+      <c r="K3" s="3">
+        <f t="shared" si="1"/>
+        <v>0.117827626918536</v>
+      </c>
+      <c r="L3" s="3">
+        <f t="shared" si="2"/>
+        <v>0.10540768905787917</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>1966</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="8">
+        <v>995.2</v>
+      </c>
+      <c r="D4" s="8">
+        <v>262</v>
+      </c>
+      <c r="E4" s="8">
+        <v>33</v>
+      </c>
+      <c r="F4" s="8">
+        <f t="shared" si="0"/>
+        <v>700.2</v>
+      </c>
+      <c r="G4" s="8">
+        <v>295</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="8">
+        <v>230</v>
+      </c>
+      <c r="J4" s="7">
+        <v>2612</v>
+      </c>
+      <c r="K4" s="3">
+        <f t="shared" si="1"/>
+        <v>0.12595419847328243</v>
+      </c>
+      <c r="L4" s="3">
+        <f t="shared" si="2"/>
+        <v>0.11186440677966102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>1967</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1006</v>
+      </c>
+      <c r="D5" s="8">
+        <v>271</v>
+      </c>
+      <c r="E5" s="8">
+        <v>33</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="0"/>
+        <v>702</v>
+      </c>
+      <c r="G5" s="8">
+        <v>304</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="8">
+        <v>230</v>
+      </c>
+      <c r="J5" s="7">
+        <v>2612</v>
+      </c>
+      <c r="K5" s="3">
+        <f t="shared" si="1"/>
+        <v>0.12177121771217712</v>
+      </c>
+      <c r="L5" s="3">
+        <f t="shared" si="2"/>
+        <v>0.10855263157894737</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>1967</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1026</v>
+      </c>
+      <c r="D6" s="5">
+        <v>267</v>
+      </c>
+      <c r="E6" s="5">
+        <v>33</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
+        <v>726</v>
+      </c>
+      <c r="G6" s="5">
+        <v>300</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="5">
+        <v>230</v>
+      </c>
+      <c r="J6" s="7">
+        <v>2612</v>
+      </c>
+      <c r="K6" s="3">
+        <f t="shared" si="1"/>
+        <v>0.12359550561797752</v>
+      </c>
+      <c r="L6" s="3">
+        <f t="shared" si="2"/>
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>1967</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1026</v>
+      </c>
+      <c r="D7" s="5">
+        <v>266</v>
+      </c>
+      <c r="E7" s="5">
+        <v>33</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>727</v>
+      </c>
+      <c r="G7" s="5">
+        <v>299</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="5">
+        <v>230</v>
+      </c>
+      <c r="J7" s="7">
+        <v>2612</v>
+      </c>
+      <c r="K7" s="3">
+        <f t="shared" si="1"/>
+        <v>0.12406015037593984</v>
+      </c>
+      <c r="L7" s="3">
+        <f t="shared" si="2"/>
+        <v>0.11036789297658862</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>1968</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1039</v>
+      </c>
+      <c r="D8" s="8">
+        <v>273</v>
+      </c>
+      <c r="E8" s="8">
+        <v>33</v>
+      </c>
+      <c r="F8" s="8">
+        <f t="shared" si="0"/>
+        <v>733</v>
+      </c>
+      <c r="G8" s="8">
+        <v>306</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="8">
+        <v>230</v>
+      </c>
+      <c r="J8" s="7">
+        <v>2612</v>
+      </c>
+      <c r="K8" s="3">
+        <f t="shared" si="1"/>
+        <v>0.12087912087912088</v>
+      </c>
+      <c r="L8" s="3">
+        <f t="shared" si="2"/>
+        <v>0.10784313725490197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>1969</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="8">
+        <v>15103</v>
+      </c>
+      <c r="D9" s="4">
+        <v>2034</v>
+      </c>
+      <c r="E9" s="8">
+        <v>4821</v>
+      </c>
+      <c r="F9" s="8">
+        <f t="shared" si="0"/>
+        <v>8248</v>
+      </c>
+      <c r="G9" s="8">
+        <f>C9-F9</f>
+        <v>6855</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="8">
+        <v>311</v>
+      </c>
+      <c r="J9" s="8">
+        <v>2261</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3702064896755162</v>
+      </c>
+      <c r="L9" s="3">
+        <f t="shared" si="2"/>
+        <v>0.70328227571115975</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>1969</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="5">
+        <v>15065</v>
+      </c>
+      <c r="D10" s="13">
+        <v>2034</v>
+      </c>
+      <c r="E10" s="5">
+        <v>4819</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" si="0"/>
+        <v>8212</v>
+      </c>
+      <c r="G10" s="5">
+        <f>C10-F10</f>
+        <v>6853</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="5">
+        <v>311</v>
+      </c>
+      <c r="J10" s="5">
+        <v>2273</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" si="1"/>
+        <v>2.3692232055063913</v>
+      </c>
+      <c r="L10" s="3">
+        <f t="shared" si="2"/>
+        <v>0.70319568072377059</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>1970</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="5">
+        <v>14916</v>
+      </c>
+      <c r="D11" s="13">
+        <v>2109</v>
+      </c>
+      <c r="E11" s="5">
+        <v>4489</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>8318</v>
+      </c>
+      <c r="G11" s="5">
+        <f>C11-F11</f>
+        <v>6598</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="5">
+        <v>311</v>
+      </c>
+      <c r="J11" s="5">
+        <v>2263</v>
+      </c>
+      <c r="K11" s="3">
+        <f t="shared" si="1"/>
+        <v>2.1284969179706024</v>
+      </c>
+      <c r="L11" s="3">
+        <f t="shared" si="2"/>
+        <v>0.68035768414671116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>1970</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5">
+        <v>5660</v>
+      </c>
+      <c r="D12" s="5">
+        <f>G12-E12</f>
+        <v>1144</v>
+      </c>
+      <c r="E12" s="5">
+        <v>756</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="0"/>
+        <v>3760</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1900</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="5">
+        <v>314</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1880</v>
+      </c>
+      <c r="K12" s="3">
+        <f t="shared" si="1"/>
+        <v>0.66083916083916083</v>
+      </c>
+      <c r="L12" s="3">
+        <f t="shared" si="2"/>
+        <v>0.39789473684210525</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>1970</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5727</v>
+      </c>
+      <c r="D13" s="8">
+        <f>G13-E13</f>
+        <v>1360</v>
+      </c>
+      <c r="E13" s="8">
+        <v>520</v>
+      </c>
+      <c r="F13" s="8">
+        <f>C13-G13</f>
+        <v>3847</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1880</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="8">
+        <v>314</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1880</v>
+      </c>
+      <c r="K13" s="3">
+        <f t="shared" si="1"/>
+        <v>0.38235294117647056</v>
+      </c>
+      <c r="L13" s="3">
+        <f t="shared" si="2"/>
+        <v>0.27659574468085107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>1971</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="5">
+        <v>16447</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2626</v>
+      </c>
+      <c r="E14" s="5">
+        <v>4795</v>
+      </c>
+      <c r="F14" s="5">
+        <f>C14-D14-E14</f>
+        <v>9026</v>
+      </c>
+      <c r="G14" s="5">
+        <f>C14-F14</f>
+        <v>7421</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="5">
+        <v>311</v>
+      </c>
+      <c r="J14" s="5">
+        <v>2250</v>
+      </c>
+      <c r="K14" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8259710586443261</v>
+      </c>
+      <c r="L14" s="3">
+        <f t="shared" si="2"/>
+        <v>0.64613933432152004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>1971</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="8">
+        <v>15034</v>
+      </c>
+      <c r="D15" s="8">
+        <v>2134</v>
+      </c>
+      <c r="E15" s="8">
+        <v>4700</v>
+      </c>
+      <c r="F15" s="8">
+        <f>C15-D15-E15</f>
+        <v>8200</v>
+      </c>
+      <c r="G15" s="8">
+        <f>C15-F15</f>
+        <v>6834</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" s="8">
+        <v>311</v>
+      </c>
+      <c r="J15" s="8">
+        <v>2263</v>
+      </c>
+      <c r="K15" s="3">
+        <f t="shared" si="1"/>
+        <v>2.202436738519213</v>
+      </c>
+      <c r="L15" s="3">
+        <f t="shared" si="2"/>
+        <v>0.68773778167983612</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>1972</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="8">
+        <v>16447</v>
+      </c>
+      <c r="D16" s="8">
+        <v>2626</v>
+      </c>
+      <c r="E16" s="8">
+        <v>4795</v>
+      </c>
+      <c r="F16" s="8">
+        <f>C16-D16-E16</f>
+        <v>9026</v>
+      </c>
+      <c r="G16" s="8">
+        <f>C16-F16</f>
+        <v>7421</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="8">
+        <v>311</v>
+      </c>
+      <c r="J16" s="8">
+        <v>2267</v>
+      </c>
+      <c r="K16" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8259710586443261</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" si="2"/>
+        <v>0.64613933432152004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>1972</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="5">
+        <v>16447</v>
+      </c>
+      <c r="D17" s="5">
+        <v>2626</v>
+      </c>
+      <c r="E17" s="5">
+        <v>4795</v>
+      </c>
+      <c r="F17" s="5">
+        <f>C17-D17-E17</f>
+        <v>9026</v>
+      </c>
+      <c r="G17" s="5">
+        <f>C17-F17</f>
+        <v>7421</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="5">
+        <v>311</v>
+      </c>
+      <c r="J17" s="5">
+        <v>2265</v>
+      </c>
+      <c r="K17" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8259710586443261</v>
+      </c>
+      <c r="L17" s="3">
+        <f t="shared" si="2"/>
+        <v>0.64613933432152004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>1972</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="5">
+        <v>5750</v>
+      </c>
+      <c r="D18" s="5">
+        <f>G18-E18</f>
+        <v>1360</v>
+      </c>
+      <c r="E18" s="5">
+        <v>520</v>
+      </c>
+      <c r="F18" s="5">
+        <f>C18-G18</f>
+        <v>3870</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1880</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="5">
+        <v>314</v>
+      </c>
+      <c r="J18" s="5">
+        <v>1880</v>
+      </c>
+      <c r="K18" s="3">
+        <f t="shared" si="1"/>
+        <v>0.38235294117647056</v>
+      </c>
+      <c r="L18" s="3">
+        <f t="shared" si="2"/>
+        <v>0.27659574468085107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>1973</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="5">
+        <v>5700</v>
+      </c>
+      <c r="D19" s="5">
+        <f>G19-E19</f>
+        <v>1000</v>
+      </c>
+      <c r="E19" s="5">
+        <v>836</v>
+      </c>
+      <c r="F19" s="5">
+        <f>C19-D19-E19</f>
+        <v>3864</v>
+      </c>
+      <c r="G19" s="5">
+        <v>1836</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="3">
+        <f t="shared" si="1"/>
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="L19" s="3">
+        <f t="shared" si="2"/>
+        <v>0.45533769063180829</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>1976</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="8">
+        <v>5795</v>
+      </c>
+      <c r="D20" s="8">
+        <f>G20-E20</f>
+        <v>1365</v>
+      </c>
+      <c r="E20" s="8">
+        <v>515</v>
+      </c>
+      <c r="F20" s="8">
+        <f>C20-G20</f>
+        <v>3915</v>
+      </c>
+      <c r="G20" s="8">
+        <v>1880</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="8">
+        <v>314</v>
+      </c>
+      <c r="J20" s="8">
+        <v>1880</v>
+      </c>
+      <c r="K20" s="3">
+        <f t="shared" si="1"/>
+        <v>0.37728937728937728</v>
+      </c>
+      <c r="L20" s="3">
+        <f t="shared" si="2"/>
+        <v>0.27393617021276595</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>2013</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="5">
+        <v>3780</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1200</v>
+      </c>
+      <c r="E21" s="5">
+        <v>170</v>
+      </c>
+      <c r="F21" s="5">
+        <v>2410</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1370</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I21" s="5">
+        <v>333</v>
+      </c>
+      <c r="J21" s="5">
+        <v>1880</v>
+      </c>
+      <c r="K21" s="3">
+        <f t="shared" si="1"/>
+        <v>0.14166666666666666</v>
+      </c>
+      <c r="L21" s="3">
+        <f t="shared" si="2"/>
+        <v>0.12408759124087591</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>2019</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="8">
+        <v>3640</v>
+      </c>
+      <c r="D22" s="8">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="8">
+        <v>170</v>
+      </c>
+      <c r="F22" s="8">
+        <v>2270</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1370</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I22" s="8">
+        <v>333</v>
+      </c>
+      <c r="J22" s="8">
+        <v>1880</v>
+      </c>
+      <c r="K22" s="3">
+        <f t="shared" si="1"/>
+        <v>0.14166666666666666</v>
+      </c>
+      <c r="L22" s="3">
+        <f t="shared" si="2"/>
+        <v>0.12408759124087591</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
+        <v>2019</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1471</v>
+      </c>
+      <c r="D23" s="5">
+        <v>626</v>
+      </c>
+      <c r="E23" s="5">
+        <v>27</v>
+      </c>
+      <c r="F23" s="5">
+        <v>818</v>
+      </c>
+      <c r="G23" s="5">
+        <v>653</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="5">
+        <v>318</v>
+      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="3">
+        <f t="shared" si="1"/>
+        <v>4.3130990415335461E-2</v>
+      </c>
+      <c r="L23" s="3">
+        <f t="shared" si="2"/>
+        <v>4.1347626339969371E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>2019</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="8">
+        <v>585</v>
+      </c>
+      <c r="D24" s="8">
+        <v>150</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="8">
+        <v>435</v>
+      </c>
+      <c r="G24" s="8">
+        <v>150</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="8">
+        <v>318</v>
+      </c>
+      <c r="J24" s="8">
+        <v>1930</v>
+      </c>
+      <c r="K24" s="3">
+        <f t="shared" si="1"/>
+        <v>6.6666666666666675E-4</v>
+      </c>
+      <c r="L24" s="3">
+        <f t="shared" si="2"/>
+        <v>6.6622251832111927E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
+        <v>2020</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="5">
+        <v>3800</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1200</v>
+      </c>
+      <c r="E25" s="5">
+        <v>800</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1800</v>
+      </c>
+      <c r="G25" s="5">
+        <v>2000</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="5">
+        <v>333</v>
+      </c>
+      <c r="J25" s="5">
+        <v>1930</v>
+      </c>
+      <c r="K25" s="3">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L25" s="3">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
+        <v>2022</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="8">
+        <v>14.6</v>
+      </c>
+      <c r="D26" s="8">
+        <v>0.7</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="F26" s="8">
+        <v>13.9</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0.69999999999999929</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8">
+        <v>2500</v>
+      </c>
+      <c r="K26" s="3">
+        <f t="shared" si="1"/>
+        <v>0.14285714285714288</v>
+      </c>
+      <c r="L26" s="3">
+        <f t="shared" si="2"/>
+        <v>0.12500000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="8">
+        <v>1750</v>
+      </c>
+      <c r="D27" s="8">
+        <v>770</v>
+      </c>
+      <c r="E27" s="8">
+        <v>30</v>
+      </c>
+      <c r="F27" s="8">
+        <v>950</v>
+      </c>
+      <c r="G27" s="8">
+        <v>800</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" s="8">
+        <v>333</v>
+      </c>
+      <c r="J27" s="7"/>
+      <c r="K27" s="3">
+        <f t="shared" si="1"/>
+        <v>3.896103896103896E-2</v>
+      </c>
+      <c r="L27" s="3">
+        <f t="shared" si="2"/>
+        <v>3.7499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
+        <v>2023</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="8">
+        <v>1000</v>
+      </c>
+      <c r="D28" s="8">
+        <v>340</v>
+      </c>
+      <c r="E28" s="8">
+        <v>30</v>
+      </c>
+      <c r="F28" s="8">
+        <v>630</v>
+      </c>
+      <c r="G28" s="8">
+        <v>370</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="8">
+        <v>333</v>
+      </c>
+      <c r="J28" s="7"/>
+      <c r="K28" s="3">
+        <f t="shared" si="1"/>
+        <v>8.8235294117647065E-2</v>
+      </c>
+      <c r="L28" s="3">
+        <f t="shared" si="2"/>
+        <v>8.1081081081081086E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>2023</v>
       </c>
@@ -3004,7 +4654,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -3037,7 +4687,7 @@
       <c r="J30" s="10"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>2024</v>
       </c>
@@ -3064,7 +4714,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -3104,18 +4754,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
-        <v>2024</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L33">
-    <sortCondition ref="A2:A33"/>
-  </sortState>
   <conditionalFormatting sqref="K2:K32">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -3141,32 +4780,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB6D447-256B-4552-8531-20A905B8B356}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -3184,7 +4823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -3226,7 +4865,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -3268,7 +4907,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -3309,7 +4948,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -3350,7 +4989,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -3391,7 +5030,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -3432,7 +5071,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -3473,7 +5112,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>1970</v>
       </c>
@@ -3515,7 +5154,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>1970</v>
       </c>
@@ -3557,7 +5196,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>1972</v>
       </c>
@@ -3599,7 +5238,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>1973</v>
       </c>
@@ -3641,7 +5280,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>1976</v>
       </c>
@@ -3683,7 +5322,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>2013</v>
       </c>
@@ -3723,7 +5362,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>2019</v>
       </c>
@@ -3763,7 +5402,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2019</v>
       </c>
@@ -3801,7 +5440,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>2019</v>
       </c>
@@ -3841,7 +5480,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>2020</v>
       </c>
@@ -3881,7 +5520,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>2022</v>
       </c>
@@ -3919,7 +5558,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>2023</v>
       </c>
@@ -3957,7 +5596,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>2023</v>
       </c>
@@ -3995,7 +5634,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -4035,7 +5674,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -4117,32 +5756,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05661A04-FF2A-413A-B709-071725466C45}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -4160,7 +5799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -4202,7 +5841,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -4244,7 +5883,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -4285,7 +5924,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1970</v>
       </c>
@@ -4327,7 +5966,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1970</v>
       </c>
@@ -4369,7 +6008,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>1973</v>
       </c>
@@ -4411,7 +6050,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>1976</v>
       </c>
@@ -4453,7 +6092,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>2019</v>
       </c>
@@ -4491,7 +6130,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>2019</v>
       </c>
@@ -4531,7 +6170,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>2020</v>
       </c>
@@ -4571,7 +6210,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>2022</v>
       </c>
@@ -4609,7 +6248,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>2023</v>
       </c>
@@ -4647,7 +6286,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>2023</v>
       </c>
@@ -4685,7 +6324,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -4725,7 +6364,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>2024</v>
       </c>

--- a/Lander DB 251 redux.xlsx
+++ b/Lander DB 251 redux.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9D9499-E3FE-42F7-9CAD-38351E354CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F79447F-9E12-41A4-8DD9-A031B9F33B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Real Landers" sheetId="1" r:id="rId1"/>
@@ -1734,7 +1734,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1754,12 +1754,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -2207,20 +2201,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.88671875" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2258,7 +2252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1966</v>
       </c>
@@ -2301,7 +2295,7 @@
       </c>
       <c r="M2" s="4"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -2344,7 +2338,7 @@
       </c>
       <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -2386,7 +2380,7 @@
       </c>
       <c r="M4" s="4"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -2428,7 +2422,7 @@
       </c>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -2470,7 +2464,7 @@
       </c>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -2512,7 +2506,7 @@
       </c>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -2554,7 +2548,7 @@
       </c>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>1969</v>
       </c>
@@ -2597,7 +2591,7 @@
       </c>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>1969</v>
       </c>
@@ -2640,7 +2634,7 @@
       </c>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1970</v>
       </c>
@@ -2683,7 +2677,7 @@
       </c>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -2726,7 +2720,7 @@
       </c>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>1970</v>
       </c>
@@ -2769,7 +2763,7 @@
       </c>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>1971</v>
       </c>
@@ -2812,7 +2806,7 @@
       </c>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>1971</v>
       </c>
@@ -2855,7 +2849,7 @@
       </c>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>1972</v>
       </c>
@@ -2898,7 +2892,7 @@
       </c>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -2941,7 +2935,7 @@
       </c>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -2984,7 +2978,7 @@
       </c>
       <c r="M18" s="4"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -3021,7 +3015,7 @@
       </c>
       <c r="M19" s="4"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -3064,7 +3058,7 @@
       </c>
       <c r="M20" s="4"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -3105,7 +3099,7 @@
       </c>
       <c r="M21" s="4"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -3146,7 +3140,7 @@
       </c>
       <c r="M22" s="4"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -3185,7 +3179,7 @@
       </c>
       <c r="M23" s="4"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -3226,7 +3220,7 @@
       </c>
       <c r="M24" s="4"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -3267,7 +3261,7 @@
       </c>
       <c r="M25" s="4"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -3306,7 +3300,7 @@
       </c>
       <c r="M26" s="4"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -3345,7 +3339,7 @@
       </c>
       <c r="M27" s="4"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -3383,7 +3377,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -3416,7 +3410,7 @@
       <c r="J29" s="10"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -3488,9 +3482,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B5FE63-1677-42A4-8B75-DD4C8D8979A4}">
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3528,7 +3522,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1966</v>
       </c>
@@ -3570,7 +3564,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -3612,7 +3606,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -3653,7 +3647,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -3694,7 +3688,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -3735,7 +3729,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -3776,7 +3770,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -3817,7 +3811,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>1969</v>
       </c>
@@ -3859,7 +3853,7 @@
         <v>0.70328227571115975</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>1969</v>
       </c>
@@ -3901,7 +3895,7 @@
         <v>0.70319568072377059</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1970</v>
       </c>
@@ -3943,7 +3937,7 @@
         <v>0.68035768414671116</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1970</v>
       </c>
@@ -3985,7 +3979,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>1970</v>
       </c>
@@ -4027,7 +4021,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>1971</v>
       </c>
@@ -4069,7 +4063,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>1971</v>
       </c>
@@ -4111,7 +4105,7 @@
         <v>0.68773778167983612</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>1972</v>
       </c>
@@ -4153,7 +4147,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>1972</v>
       </c>
@@ -4195,7 +4189,7 @@
         <v>0.64613933432152004</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>1972</v>
       </c>
@@ -4237,7 +4231,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>1973</v>
       </c>
@@ -4273,7 +4267,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>1976</v>
       </c>
@@ -4315,7 +4309,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2013</v>
       </c>
@@ -4355,7 +4349,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <v>2019</v>
       </c>
@@ -4395,7 +4389,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2019</v>
       </c>
@@ -4433,7 +4427,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <v>2019</v>
       </c>
@@ -4473,7 +4467,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2020</v>
       </c>
@@ -4513,7 +4507,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>2022</v>
       </c>
@@ -4551,7 +4545,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>2023</v>
       </c>
@@ -4589,7 +4583,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <v>2023</v>
       </c>
@@ -4627,7 +4621,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2023</v>
       </c>
@@ -4654,7 +4648,7 @@
       <c r="J29" s="7"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -4687,7 +4681,7 @@
       <c r="J30" s="10"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <v>2024</v>
       </c>
@@ -4714,7 +4708,7 @@
       <c r="J31" s="7"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -4783,9 +4777,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB6D447-256B-4552-8531-20A905B8B356}">
   <dimension ref="A1:L23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4823,7 +4817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -4865,7 +4859,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -4907,7 +4901,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -4948,7 +4942,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>1967</v>
       </c>
@@ -4989,7 +4983,7 @@
         <v>0.10855263157894737</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>1967</v>
       </c>
@@ -5030,7 +5024,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1967</v>
       </c>
@@ -5071,7 +5065,7 @@
         <v>0.11036789297658862</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1968</v>
       </c>
@@ -5112,7 +5106,7 @@
         <v>0.10784313725490197</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>1970</v>
       </c>
@@ -5154,7 +5148,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>1970</v>
       </c>
@@ -5196,7 +5190,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>1972</v>
       </c>
@@ -5238,7 +5232,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>1973</v>
       </c>
@@ -5280,7 +5274,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>1976</v>
       </c>
@@ -5322,7 +5316,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>2013</v>
       </c>
@@ -5362,7 +5356,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>2019</v>
       </c>
@@ -5402,7 +5396,7 @@
         <v>0.12408759124087591</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2019</v>
       </c>
@@ -5440,7 +5434,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>2019</v>
       </c>
@@ -5480,7 +5474,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>2020</v>
       </c>
@@ -5520,7 +5514,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>2022</v>
       </c>
@@ -5558,7 +5552,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>2023</v>
       </c>
@@ -5596,7 +5590,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>2023</v>
       </c>
@@ -5634,7 +5628,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -5674,7 +5668,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -5759,9 +5753,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05661A04-FF2A-413A-B709-071725466C45}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5799,7 +5793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1966</v>
       </c>
@@ -5841,7 +5835,7 @@
         <v>0.12280701754385964</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1966</v>
       </c>
@@ -5883,7 +5877,7 @@
         <v>0.10540768905787917</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="8">
         <v>1966</v>
       </c>
@@ -5924,7 +5918,7 @@
         <v>0.11186440677966102</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>1970</v>
       </c>
@@ -5966,7 +5960,7 @@
         <v>0.39789473684210525</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>1970</v>
       </c>
@@ -6008,7 +6002,7 @@
         <v>0.27659574468085107</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1973</v>
       </c>
@@ -6050,7 +6044,7 @@
         <v>0.45533769063180829</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>1976</v>
       </c>
@@ -6092,7 +6086,7 @@
         <v>0.27393617021276595</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2019</v>
       </c>
@@ -6130,7 +6124,7 @@
         <v>4.1347626339969371E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>2019</v>
       </c>
@@ -6170,7 +6164,7 @@
         <v>6.6622251832111927E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>2020</v>
       </c>
@@ -6210,7 +6204,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
         <v>2022</v>
       </c>
@@ -6248,7 +6242,7 @@
         <v>0.12500000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>2023</v>
       </c>
@@ -6286,7 +6280,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>2023</v>
       </c>
@@ -6324,7 +6318,7 @@
         <v>8.1081081081081086E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -6364,7 +6358,7 @@
         <v>9.5238095238095233E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2024</v>
       </c>
